--- a/BACKEND/Groups.xlsx
+++ b/BACKEND/Groups.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76E13A27-BBB3-444C-B045-EBD34E7F91B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1D94AFB-B08F-40AB-A790-1EA40D9532D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="525" yWindow="5715" windowWidth="28800" windowHeight="15885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="97">
   <si>
     <t>גוויס</t>
   </si>
@@ -305,6 +305,15 @@
   </si>
   <si>
     <t>תנורים מאווררים</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>גופי תאורה</t>
+  </si>
+  <si>
+    <t>תעשייה</t>
   </si>
 </sst>
 </file>
@@ -646,15 +655,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C80"/>
+  <dimension ref="A1:D80"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.5703125" customWidth="1"/>
     <col min="2" max="2" width="68" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="39.5703125" customWidth="1"/>
+    <col min="4" max="4" width="29.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>66</v>
       </c>
@@ -664,8 +674,11 @@
       <c r="C1" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -675,8 +688,11 @@
       <c r="C2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>71</v>
       </c>
@@ -686,8 +702,11 @@
       <c r="C3" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>37</v>
       </c>
@@ -697,8 +716,11 @@
       <c r="C4" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>12</v>
       </c>
@@ -708,8 +730,11 @@
       <c r="C5" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>16</v>
       </c>
@@ -719,8 +744,11 @@
       <c r="C6" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>8</v>
       </c>
@@ -730,8 +758,11 @@
       <c r="C7" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D7" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>46</v>
       </c>
@@ -741,8 +772,11 @@
       <c r="C8" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D8" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>10</v>
       </c>
@@ -752,8 +786,11 @@
       <c r="C9" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D9" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>44</v>
       </c>
@@ -763,8 +800,11 @@
       <c r="C10" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D10" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>21</v>
       </c>
@@ -774,8 +814,11 @@
       <c r="C11" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D11" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>35</v>
       </c>
@@ -785,8 +828,11 @@
       <c r="C12" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D12" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>6</v>
       </c>
@@ -796,8 +842,11 @@
       <c r="C13" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D13" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>7</v>
       </c>
@@ -807,8 +856,11 @@
       <c r="C14" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D14" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>45</v>
       </c>
@@ -818,16 +870,22 @@
       <c r="C15" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D15" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>9</v>
       </c>
       <c r="B16" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>2</v>
       </c>
@@ -837,8 +895,11 @@
       <c r="C17" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>11</v>
       </c>
@@ -848,8 +909,11 @@
       <c r="C18" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D18" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>5</v>
       </c>
@@ -859,8 +923,11 @@
       <c r="C19" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D19" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>40</v>
       </c>
@@ -870,8 +937,11 @@
       <c r="C20" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D20" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>42</v>
       </c>
@@ -881,8 +951,11 @@
       <c r="C21" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D21" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>25</v>
       </c>
@@ -892,8 +965,11 @@
       <c r="C22" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D22" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>15</v>
       </c>
@@ -903,8 +979,11 @@
       <c r="C23" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D23" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>13</v>
       </c>
@@ -914,8 +993,11 @@
       <c r="C24" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D24" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>14</v>
       </c>
@@ -925,8 +1007,11 @@
       <c r="C25" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D25" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>75</v>
       </c>
@@ -936,8 +1021,11 @@
       <c r="C26" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D26" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>17</v>
       </c>
@@ -947,8 +1035,11 @@
       <c r="C27" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D27" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>19</v>
       </c>
@@ -958,8 +1049,11 @@
       <c r="C28" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D28" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26</v>
       </c>
@@ -969,8 +1063,11 @@
       <c r="C29" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D29" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>18</v>
       </c>
@@ -980,8 +1077,11 @@
       <c r="C30" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D30" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>20</v>
       </c>
@@ -991,8 +1091,11 @@
       <c r="C31" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D31" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>22</v>
       </c>
@@ -1002,8 +1105,11 @@
       <c r="C32" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D32" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>23</v>
       </c>
@@ -1013,8 +1119,11 @@
       <c r="C33" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D33" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>24</v>
       </c>
@@ -1024,8 +1133,11 @@
       <c r="C34" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D34" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>28</v>
       </c>
@@ -1035,8 +1147,11 @@
       <c r="C35" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D35" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>29</v>
       </c>
@@ -1046,8 +1161,11 @@
       <c r="C36" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D36" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>30</v>
       </c>
@@ -1057,8 +1175,11 @@
       <c r="C37" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D37" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>31</v>
       </c>
@@ -1068,8 +1189,11 @@
       <c r="C38" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D38" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>32</v>
       </c>
@@ -1079,8 +1203,11 @@
       <c r="C39" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D39" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>33</v>
       </c>
@@ -1090,8 +1217,11 @@
       <c r="C40" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D40" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>34</v>
       </c>
@@ -1101,8 +1231,11 @@
       <c r="C41" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D41" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>58</v>
       </c>
@@ -1112,8 +1245,11 @@
       <c r="C42" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D42" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>83</v>
       </c>
@@ -1123,8 +1259,11 @@
       <c r="C43" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D43" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>27</v>
       </c>
@@ -1134,8 +1273,11 @@
       <c r="C44" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D44" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>98</v>
       </c>
@@ -1145,8 +1287,11 @@
       <c r="C45" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D45" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>59</v>
       </c>
@@ -1156,8 +1301,11 @@
       <c r="C46" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D46" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>60</v>
       </c>
@@ -1167,8 +1315,11 @@
       <c r="C47" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D47" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>51</v>
       </c>
@@ -1178,8 +1329,11 @@
       <c r="C48" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D48" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>64</v>
       </c>
@@ -1189,8 +1343,11 @@
       <c r="C49" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D49" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>65</v>
       </c>
@@ -1200,8 +1357,11 @@
       <c r="C50" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D50" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>52</v>
       </c>
@@ -1211,8 +1371,11 @@
       <c r="C51" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D51" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>54</v>
       </c>
@@ -1222,8 +1385,11 @@
       <c r="C52" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D52" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>55</v>
       </c>
@@ -1233,8 +1399,11 @@
       <c r="C53" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D53" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>56</v>
       </c>
@@ -1244,8 +1413,11 @@
       <c r="C54" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D54" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>57</v>
       </c>
@@ -1255,8 +1427,11 @@
       <c r="C55" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D55" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>3</v>
       </c>
@@ -1266,8 +1441,11 @@
       <c r="C56" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D56" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>4</v>
       </c>
@@ -1277,8 +1455,11 @@
       <c r="C57" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D57" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>92</v>
       </c>
@@ -1288,8 +1469,11 @@
       <c r="C58" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D58" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>85</v>
       </c>
@@ -1299,8 +1483,11 @@
       <c r="C59" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D59" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>61</v>
       </c>
@@ -1310,8 +1497,11 @@
       <c r="C60" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D60" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>62</v>
       </c>
@@ -1321,8 +1511,11 @@
       <c r="C61" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D61" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>66</v>
       </c>
@@ -1332,8 +1525,11 @@
       <c r="C62" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D62" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>63</v>
       </c>
@@ -1343,8 +1539,11 @@
       <c r="C63" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D63" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>73</v>
       </c>
@@ -1354,8 +1553,11 @@
       <c r="C64" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D64" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>72</v>
       </c>
@@ -1365,8 +1567,11 @@
       <c r="C65" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D65" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>81</v>
       </c>
@@ -1376,8 +1581,11 @@
       <c r="C66" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D66" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>84</v>
       </c>
@@ -1387,8 +1595,11 @@
       <c r="C67" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D67" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>76</v>
       </c>
@@ -1398,8 +1609,11 @@
       <c r="C68" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D68" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>77</v>
       </c>
@@ -1409,8 +1623,11 @@
       <c r="C69" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D69" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>80</v>
       </c>
@@ -1420,8 +1637,11 @@
       <c r="C70" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D70" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>82</v>
       </c>
@@ -1431,8 +1651,11 @@
       <c r="C71" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D71" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>86</v>
       </c>
@@ -1442,8 +1665,11 @@
       <c r="C72" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D72" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>88</v>
       </c>
@@ -1453,8 +1679,11 @@
       <c r="C73" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D73" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>95</v>
       </c>
@@ -1464,8 +1693,11 @@
       <c r="C74" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D74" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>96</v>
       </c>
@@ -1475,8 +1707,11 @@
       <c r="C75" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D75" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>101</v>
       </c>
@@ -1486,8 +1721,11 @@
       <c r="C76" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D76" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>97</v>
       </c>
@@ -1497,8 +1735,11 @@
       <c r="C77" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D77" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>87</v>
       </c>
@@ -1508,8 +1749,11 @@
       <c r="C78" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D78" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>102</v>
       </c>
@@ -1519,8 +1763,11 @@
       <c r="C79" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D79" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>200</v>
       </c>
@@ -1529,6 +1776,9 @@
       </c>
       <c r="C80" t="s">
         <v>93</v>
+      </c>
+      <c r="D80" t="s">
+        <v>91</v>
       </c>
     </row>
   </sheetData>
